--- a/정기/BM/각아이템 가치.xlsx
+++ b/정기/BM/각아이템 가치.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\BM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4D12ED-F380-4B8D-9A95-14CAF792E5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA2367-6268-4819-92A8-59A3A09E5FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="720" windowWidth="14955" windowHeight="15480" xr2:uid="{9AFA1BF2-6409-49D5-B0ED-3502A233A019}"/>
+    <workbookView xWindow="40485" yWindow="660" windowWidth="19125" windowHeight="15480" xr2:uid="{9AFA1BF2-6409-49D5-B0ED-3502A233A019}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>가속 1h</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,14 @@
   </si>
   <si>
     <t>가속소환권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2만원기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만원기준</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -78,7 +86,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,6 +105,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -103,7 +122,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -111,18 +130,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -455,13 +505,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E92CFC-541C-4BF7-97E3-F34670683D01}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,7 +521,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -477,7 +529,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -485,7 +537,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -493,7 +545,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -501,7 +553,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -509,22 +561,86 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
         <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4">
+        <v>440000</v>
+      </c>
+      <c r="C13" s="4">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="B14" s="4">
+        <v>370000</v>
+      </c>
+      <c r="C14" s="4">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>7</v>
+      </c>
+      <c r="B15" s="4">
+        <v>300000</v>
+      </c>
+      <c r="C15" s="4">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B16" s="4">
+        <v>110000</v>
+      </c>
+      <c r="C16" s="4">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4">
+        <v>44000</v>
+      </c>
+      <c r="C17" s="4">
+        <v>22000</v>
       </c>
     </row>
   </sheetData>
